--- a/evaluation/bgw-monarch-summary-data/OriginalGraphs.xlsx
+++ b/evaluation/bgw-monarch-summary-data/OriginalGraphs.xlsx
@@ -1,20 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jesualdo/Documents/GitHub/oquare-kg/evaluation/bgw-monarch-summary-data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABAD1EAA-69DB-4A47-9419-B856B9547DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="600" windowWidth="44800" windowHeight="22800" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Characteristics" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Subcharacteristics" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="Metrics" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="RawMetrics" sheetId="4" r:id="rId8"/>
+    <sheet name="Characteristics" sheetId="1" r:id="rId1"/>
+    <sheet name="Subcharacteristics" sheetId="2" r:id="rId2"/>
+    <sheet name="Metrics" sheetId="3" r:id="rId3"/>
+    <sheet name="RawMetrics" sheetId="4" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="63">
   <si>
     <t>graph</t>
   </si>
@@ -203,27 +212,26 @@
   </si>
   <si>
     <t>all</t>
-  </si>
-  <si>
-    <t>set()</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -234,61 +242,48 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -478,17 +473,20 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -514,279 +512,280 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B2" s="2">
-        <v>4.05396825396825</v>
+        <v>4.0539682539682502</v>
       </c>
       <c r="C2" s="2">
         <v>3.61666666666666</v>
       </c>
       <c r="D2" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E2" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="2">
         <v>2.5</v>
       </c>
       <c r="H2" s="2">
-        <v>2.33333333333333</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>2.3333333333333299</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B3" s="2">
-        <v>3.76825396825396</v>
+        <v>3.7682539682539602</v>
       </c>
       <c r="C3" s="2">
         <v>3.11666666666666</v>
       </c>
       <c r="D3" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E3" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="2">
         <v>2.25</v>
       </c>
       <c r="H3" s="2">
-        <v>2.33333333333333</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>2.3333333333333299</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B4" s="2">
-        <v>3.93968253968254</v>
+        <v>3.9396825396825399</v>
       </c>
       <c r="C4" s="2">
-        <v>3.76166666666666</v>
+        <v>3.7616666666666601</v>
       </c>
       <c r="D4" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E4" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H4" s="2">
-        <v>2.33333333333333</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>2.3333333333333299</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B5" s="2">
-        <v>3.93968253968254</v>
+        <v>3.9396825396825399</v>
       </c>
       <c r="C5" s="2">
-        <v>3.73666666666666</v>
+        <v>3.7366666666666601</v>
       </c>
       <c r="D5" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E5" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H5" s="2">
-        <v>2.33333333333333</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>2.3333333333333299</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>57</v>
       </c>
       <c r="B6" s="2">
-        <v>3.93968253968254</v>
+        <v>3.9396825396825399</v>
       </c>
       <c r="C6" s="2">
-        <v>3.745</v>
+        <v>3.7450000000000001</v>
       </c>
       <c r="D6" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E6" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H6" s="2">
-        <v>2.33333333333333</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>2.3333333333333299</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B7" s="2">
-        <v>3.71111111111111</v>
+        <v>3.7111111111111099</v>
       </c>
       <c r="C7" s="2">
-        <v>2.79333333333333</v>
+        <v>2.7933333333333299</v>
       </c>
       <c r="D7" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E7" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H7" s="2">
-        <v>1.66666666666666</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>1.6666666666666601</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
         <v>59</v>
       </c>
       <c r="B8" s="2">
-        <v>3.76825396825396</v>
+        <v>3.7682539682539602</v>
       </c>
       <c r="C8" s="2">
-        <v>2.19166666666666</v>
+        <v>2.1916666666666602</v>
       </c>
       <c r="D8" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E8" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H8" s="2">
-        <v>1.66666666666666</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>1.6666666666666601</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
         <v>60</v>
       </c>
       <c r="B9" s="2">
-        <v>3.71111111111111</v>
+        <v>3.7111111111111099</v>
       </c>
       <c r="C9" s="2">
         <v>2.21</v>
       </c>
       <c r="D9" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E9" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H9" s="2">
-        <v>1.66666666666666</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>1.6666666666666601</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
         <v>61</v>
       </c>
       <c r="B10" s="2">
-        <v>3.88253968253968</v>
+        <v>3.8825396825396798</v>
       </c>
       <c r="C10" s="2">
         <v>2.78833333333333</v>
       </c>
       <c r="D10" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E10" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H10" s="2">
-        <v>1.66666666666666</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>1.6666666666666601</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
         <v>62</v>
       </c>
       <c r="B11" s="2">
-        <v>3.88253968253968</v>
+        <v>3.8825396825396798</v>
       </c>
       <c r="C11" s="2">
         <v>2.78833333333333</v>
       </c>
       <c r="D11" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E11" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H11" s="2">
-        <v>1.66666666666666</v>
+        <v>1.6666666666666601</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:Q11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -839,133 +838,133 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B2" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3">
-        <v>4.85714285714285</v>
+        <v>4.8571428571428497</v>
       </c>
       <c r="E2" s="3">
-        <v>3.66666666666666</v>
+        <v>3.6666666666666599</v>
       </c>
       <c r="F2" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G2" s="3">
         <v>4.8</v>
       </c>
       <c r="H2" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="I2" s="3">
         <v>2.75</v>
       </c>
       <c r="J2" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="K2" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L2" s="3">
-        <v>4.33333333333333</v>
+        <v>4.3333333333333304</v>
       </c>
       <c r="M2" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N2" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="O2" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="P2" s="3">
         <v>2.5</v>
       </c>
       <c r="Q2" s="3">
-        <v>2.33333333333333</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>2.3333333333333299</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B3" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="D3" s="3">
-        <v>4.14285714285714</v>
+        <v>4.1428571428571397</v>
       </c>
       <c r="E3" s="3">
-        <v>3.66666666666666</v>
+        <v>3.6666666666666599</v>
       </c>
       <c r="F3" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G3" s="3">
         <v>3.8</v>
       </c>
       <c r="H3" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="I3" s="3">
         <v>2.25</v>
       </c>
       <c r="J3" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="K3" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L3" s="3">
-        <v>3.33333333333333</v>
+        <v>3.3333333333333299</v>
       </c>
       <c r="M3" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N3" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="O3" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="P3" s="3">
         <v>2.25</v>
       </c>
       <c r="Q3" s="3">
-        <v>2.33333333333333</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>2.3333333333333299</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B4" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="D4" s="3">
-        <v>4.57142857142857</v>
+        <v>4.5714285714285703</v>
       </c>
       <c r="E4" s="3">
-        <v>3.66666666666666</v>
+        <v>3.6666666666666599</v>
       </c>
       <c r="F4" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G4" s="3">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="H4" s="3">
         <v>3.6</v>
@@ -974,51 +973,51 @@
         <v>4.375</v>
       </c>
       <c r="J4" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="K4" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L4" s="3">
-        <v>3.83333333333333</v>
+        <v>3.8333333333333299</v>
       </c>
       <c r="M4" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N4" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="O4" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="P4" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="Q4" s="3">
-        <v>2.33333333333333</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>2.3333333333333299</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B5" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="D5" s="3">
-        <v>4.57142857142857</v>
+        <v>4.5714285714285703</v>
       </c>
       <c r="E5" s="3">
-        <v>3.66666666666666</v>
+        <v>3.6666666666666599</v>
       </c>
       <c r="F5" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G5" s="3">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="H5" s="3">
         <v>3.6</v>
@@ -1027,51 +1026,51 @@
         <v>4.25</v>
       </c>
       <c r="J5" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="K5" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L5" s="3">
-        <v>3.83333333333333</v>
+        <v>3.8333333333333299</v>
       </c>
       <c r="M5" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N5" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="O5" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="P5" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="Q5" s="3">
-        <v>2.33333333333333</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>2.3333333333333299</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B6" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="D6" s="3">
-        <v>4.57142857142857</v>
+        <v>4.5714285714285703</v>
       </c>
       <c r="E6" s="3">
-        <v>3.66666666666666</v>
+        <v>3.6666666666666599</v>
       </c>
       <c r="F6" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G6" s="3">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="H6" s="3">
         <v>3.6</v>
@@ -1080,48 +1079,48 @@
         <v>4.125</v>
       </c>
       <c r="J6" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="K6" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L6" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="M6" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N6" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="O6" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="P6" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="Q6" s="3">
-        <v>2.33333333333333</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>2.3333333333333299</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B7" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C7" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="D7" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E7" s="3">
-        <v>3.66666666666666</v>
+        <v>3.6666666666666599</v>
       </c>
       <c r="F7" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G7" s="3">
         <v>3.6</v>
@@ -1130,104 +1129,104 @@
         <v>2.8</v>
       </c>
       <c r="I7" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J7" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K7" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="3">
-        <v>3.16666666666666</v>
+        <v>3.1666666666666599</v>
       </c>
       <c r="M7" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N7" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="O7" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="P7" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="Q7" s="3">
-        <v>1.66666666666666</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>1.6666666666666601</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
         <v>59</v>
       </c>
       <c r="B8" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C8" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="D8" s="3">
-        <v>4.14285714285714</v>
+        <v>4.1428571428571397</v>
       </c>
       <c r="E8" s="3">
-        <v>3.66666666666666</v>
+        <v>3.6666666666666599</v>
       </c>
       <c r="F8" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G8" s="3">
         <v>3.8</v>
       </c>
       <c r="H8" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="I8" s="3">
         <v>3.125</v>
       </c>
       <c r="J8" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="3">
-        <v>2.83333333333333</v>
+        <v>2.8333333333333299</v>
       </c>
       <c r="M8" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N8" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="O8" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="P8" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="Q8" s="3">
-        <v>1.66666666666666</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>1.6666666666666601</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B9" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C9" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E9" s="3">
-        <v>3.66666666666666</v>
+        <v>3.6666666666666599</v>
       </c>
       <c r="F9" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G9" s="3">
         <v>3.6</v>
@@ -1242,45 +1241,45 @@
         <v>1.5</v>
       </c>
       <c r="K9" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="3">
         <v>2.5</v>
       </c>
       <c r="M9" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N9" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="O9" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="P9" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="Q9" s="3">
-        <v>1.66666666666666</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>1.6666666666666601</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B10" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C10" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>4.42857142857142</v>
+        <v>4.4285714285714199</v>
       </c>
       <c r="E10" s="3">
-        <v>3.66666666666666</v>
+        <v>3.6666666666666599</v>
       </c>
       <c r="F10" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G10" s="3">
         <v>4.2</v>
@@ -1295,45 +1294,45 @@
         <v>2.5</v>
       </c>
       <c r="K10" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="3">
-        <v>3.66666666666666</v>
+        <v>3.6666666666666599</v>
       </c>
       <c r="M10" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N10" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="O10" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="P10" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="Q10" s="3">
-        <v>1.66666666666666</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>1.6666666666666601</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
         <v>62</v>
       </c>
       <c r="B11" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C11" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="D11" s="3">
-        <v>4.42857142857142</v>
+        <v>4.4285714285714199</v>
       </c>
       <c r="E11" s="3">
-        <v>3.66666666666666</v>
+        <v>3.6666666666666599</v>
       </c>
       <c r="F11" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G11" s="3">
         <v>4.2</v>
@@ -1348,43 +1347,44 @@
         <v>2.5</v>
       </c>
       <c r="K11" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="3">
-        <v>3.66666666666666</v>
+        <v>3.6666666666666599</v>
       </c>
       <c r="M11" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N11" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="O11" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="P11" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="Q11" s="3">
-        <v>1.66666666666666</v>
+        <v>1.6666666666666601</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:AC11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="8" max="8" width="16.75"/>
+    <col min="8" max="8" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -1473,909 +1473,910 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B2" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C2" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E2" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F2" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G2" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H2" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K2" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L2" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="M2" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N2" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O2" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="P2" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="Q2" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="R2" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S2" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="T2" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="U2" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="V2" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="W2" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="X2" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="Y2" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="Z2" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="AA2" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="AB2" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="AC2" s="2">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B3" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C3" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G3" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H3" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="I3" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K3" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L3" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="M3" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N3" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="O3" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P3" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="Q3" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R3" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S3" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="T3" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="U3" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="V3" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="W3" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="X3" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="Y3" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="Z3" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="AA3" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="AB3" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="AC3" s="2">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B4" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C4" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E4" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G4" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H4" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="I4" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K4" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L4" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="M4" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N4" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O4" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P4" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="Q4" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="R4" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S4" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="T4" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="U4" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="W4" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="X4" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="Y4" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="Z4" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="AA4" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="AB4" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="AC4" s="2">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B5" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C5" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E5" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F5" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G5" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H5" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="I5" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K5" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L5" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="M5" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N5" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O5" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P5" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="Q5" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="R5" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S5" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="T5" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="U5" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="V5" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="W5" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="X5" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="Y5" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="Z5" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="AA5" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="AB5" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="AC5" s="2">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>57</v>
       </c>
       <c r="B6" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C6" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E6" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G6" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H6" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="I6" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K6" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L6" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="M6" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N6" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O6" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P6" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="Q6" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="R6" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S6" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="T6" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="U6" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="V6" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="W6" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="X6" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="Y6" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="Z6" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="AA6" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="AB6" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="AC6" s="2">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B7" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C7" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E7" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F7" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G7" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H7" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="I7" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="K7" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="L7" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="M7" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N7" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="O7" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="P7" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="Q7" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R7" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S7" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="T7" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="U7" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="V7" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="W7" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="X7" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="Y7" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="Z7" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="AA7" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="AB7" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="AC7" s="2">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
         <v>59</v>
       </c>
       <c r="B8" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C8" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E8" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F8" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G8" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H8" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="I8" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K8" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="M8" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N8" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="O8" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="P8" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="Q8" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R8" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S8" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="T8" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="U8" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="V8" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="W8" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="X8" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="Y8" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="Z8" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="AA8" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="AB8" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="AC8" s="2">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
         <v>60</v>
       </c>
       <c r="B9" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C9" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E9" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F9" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G9" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H9" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="I9" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="K9" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="L9" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="M9" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N9" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="O9" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="P9" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="Q9" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R9" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S9" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="T9" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="U9" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="W9" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="X9" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="Y9" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="Z9" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="AA9" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="AB9" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="AC9" s="2">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
         <v>61</v>
       </c>
       <c r="B10" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C10" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E10" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F10" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G10" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H10" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="I10" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K10" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L10" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="M10" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N10" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="O10" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="P10" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="Q10" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R10" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S10" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="T10" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="U10" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="W10" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="X10" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="Y10" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="Z10" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="AA10" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="AB10" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="AC10" s="2">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
         <v>62</v>
       </c>
       <c r="B11" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C11" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E11" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F11" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G11" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H11" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="I11" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K11" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L11" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="M11" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N11" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="O11" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="P11" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="Q11" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R11" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S11" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="T11" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="U11" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="W11" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="X11" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="Y11" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="Z11" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="AA11" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="AB11" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="AC11" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:AC11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -2464,274 +2465,274 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B2" s="2">
-        <v>5.23250564334086</v>
+        <v>5.2325056433408603</v>
       </c>
       <c r="C2" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D2" s="2">
-        <v>1.33408577878104</v>
+        <v>1.3340857787810401</v>
       </c>
       <c r="E2" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2">
-        <v>0.517241379310345</v>
+        <v>0.51724137931034497</v>
       </c>
       <c r="H2" s="2">
-        <v>0.134687735139202</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>63</v>
+        <v>0.13468773513920199</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0</v>
       </c>
       <c r="J2" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L2" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="b">
         <v>0</v>
       </c>
       <c r="N2" s="2">
-        <v>0.334085778781038</v>
+        <v>0.33408577878103801</v>
       </c>
       <c r="O2" s="2">
-        <v>0.865312264860798</v>
+        <v>0.86531226486079804</v>
       </c>
       <c r="P2" s="2">
-        <v>0.493604213694507</v>
+        <v>0.49360421369450702</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.510158013544018</v>
+        <v>0.51015801354401802</v>
       </c>
       <c r="R2" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S2" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="T2" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="U2" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="V2" s="2">
-        <v>1.17456734386757</v>
+        <v>1.1745673438675699</v>
       </c>
       <c r="W2" s="2">
         <v>10.9954853273138</v>
       </c>
       <c r="X2" s="2">
-        <v>0.848484848484849</v>
+        <v>0.84848484848484895</v>
       </c>
       <c r="Y2" s="2">
         <v>3.92325056433409</v>
       </c>
       <c r="Z2" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.00161786963102135</v>
+        <v>1.6178696310213501E-3</v>
       </c>
       <c r="AB2" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="AC2" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B3" s="2">
-        <v>2.49272467902996</v>
+        <v>2.4927246790299602</v>
       </c>
       <c r="C3" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D3" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2">
-        <v>0.335960858929057</v>
+        <v>0.33596085892905703</v>
       </c>
       <c r="H3" s="2">
-        <v>0.278174037089872</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>63</v>
+        <v>0.27817403708987198</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
       </c>
       <c r="J3" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L3" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="N3" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O3" s="2">
-        <v>0.721825962910128</v>
+        <v>0.72182596291012802</v>
       </c>
       <c r="P3" s="2">
-        <v>0.696433666191156</v>
+        <v>0.69643366619115599</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.748359486447931</v>
+        <v>0.74835948644793104</v>
       </c>
       <c r="R3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S3" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="T3" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="U3" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2">
-        <v>0.303566333808845</v>
+        <v>0.30356633380884501</v>
       </c>
       <c r="W3" s="2">
         <v>14.0984308131241</v>
       </c>
       <c r="X3" s="2">
-        <v>0.861111111111111</v>
+        <v>0.86111111111111105</v>
       </c>
       <c r="Y3" s="2">
-        <v>1.91098430813124</v>
+        <v>1.9109843081312401</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.966333808844508</v>
+        <v>0.96633380884450804</v>
       </c>
       <c r="AA3" s="2">
-        <v>6.18721793565293E-4</v>
+        <v>6.1872179356529304E-4</v>
       </c>
       <c r="AB3" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="AC3" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B4" s="2">
-        <v>7.9067320552831</v>
+        <v>7.9067320552830997</v>
       </c>
       <c r="C4" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D4" s="2">
         <v>1.16032099866251</v>
       </c>
       <c r="E4" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G4" s="2">
-        <v>0.998665599145983</v>
+        <v>0.99866559914598296</v>
       </c>
       <c r="H4" s="2">
-        <v>0.674543022737405</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>63</v>
+        <v>0.67454302273740496</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
       </c>
       <c r="J4" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L4" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="b">
         <v>0</v>
       </c>
       <c r="N4" s="2">
-        <v>0.160320998662506</v>
+        <v>0.16032099866250599</v>
       </c>
       <c r="O4" s="2">
-        <v>0.325456977262595</v>
+        <v>0.32545697726259498</v>
       </c>
       <c r="P4" s="2">
         <v>1.78332590280874E-4</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.19589835042354</v>
+        <v>0.19589835042354001</v>
       </c>
       <c r="R4" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S4" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="T4" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="U4" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="V4" s="2">
-        <v>1.32046366473473</v>
+        <v>1.3204636647347301</v>
       </c>
       <c r="W4" s="2">
-        <v>6.52135532768613</v>
+        <v>6.5213553276861296</v>
       </c>
       <c r="X4" s="2">
-        <v>0.923076923076923</v>
+        <v>0.92307692307692302</v>
       </c>
       <c r="Y4" s="2">
-        <v>5.91172536781097</v>
+        <v>5.9117253678109698</v>
       </c>
       <c r="Z4" s="2">
-        <v>0.918502006241641</v>
+        <v>0.91850200624164102</v>
       </c>
       <c r="AA4" s="2">
         <v>1.14524579837948E-4</v>
       </c>
       <c r="AB4" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="AC4" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>53</v>
       </c>
@@ -2739,34 +2740,34 @@
         <v>7.72536079483646</v>
       </c>
       <c r="C5" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D5" s="2">
-        <v>1.15969250852129</v>
+        <v>1.1596925085212899</v>
       </c>
       <c r="E5" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2">
-        <v>0.999166847786713</v>
+        <v>0.99916684778671305</v>
       </c>
       <c r="H5" s="2">
-        <v>0.635687867140474</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>63</v>
+        <v>0.63568786714047398</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
       </c>
       <c r="J5" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L5" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="b">
         <v>0</v>
@@ -2775,87 +2776,87 @@
         <v>0.159692508521285</v>
       </c>
       <c r="O5" s="2">
-        <v>0.364312132859526</v>
+        <v>0.36431213285952602</v>
       </c>
       <c r="P5" s="2">
-        <v>3.62607875843063E-4</v>
+        <v>3.6260787584306298E-4</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.207230401044311</v>
+        <v>0.20723040104431101</v>
       </c>
       <c r="R5" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S5" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="T5" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="U5" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="V5" s="2">
         <v>1.31902240916673</v>
       </c>
       <c r="W5" s="2">
-        <v>6.56762636884473</v>
+        <v>6.5676263688447296</v>
       </c>
       <c r="X5" s="2">
-        <v>0.928571428571429</v>
+        <v>0.92857142857142905</v>
       </c>
       <c r="Y5" s="2">
-        <v>5.77065051852926</v>
+        <v>5.7706505185292603</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.895786496482704</v>
+        <v>0.89578649648270403</v>
       </c>
       <c r="AA5" s="4">
-        <v>4.54053298871852E-5</v>
+        <v>4.5405329887185199E-5</v>
       </c>
       <c r="AB5" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="AC5" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>57</v>
       </c>
       <c r="B6" s="2">
-        <v>6.94539527302364</v>
+        <v>6.9453952730236397</v>
       </c>
       <c r="C6" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D6" s="2">
-        <v>1.14356968215159</v>
+        <v>1.1435696821515899</v>
       </c>
       <c r="E6" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G6" s="2">
-        <v>0.898898250162022</v>
+        <v>0.89889825016202196</v>
       </c>
       <c r="H6" s="2">
-        <v>0.571507742461288</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>63</v>
+        <v>0.57150774246128799</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
       </c>
       <c r="J6" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K6" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L6" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="b">
         <v>0</v>
@@ -2864,497 +2865,497 @@
         <v>0.143569682151589</v>
       </c>
       <c r="O6" s="2">
-        <v>0.428492257538712</v>
+        <v>0.42849225753871201</v>
       </c>
       <c r="P6" s="2">
         <v>0.101287693561532</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.287269763651182</v>
+        <v>0.28726976365118201</v>
       </c>
       <c r="R6" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S6" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="T6" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="U6" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="V6" s="2">
         <v>1.18585167074165</v>
       </c>
       <c r="W6" s="2">
-        <v>7.61659331703341</v>
+        <v>7.6165933170334101</v>
       </c>
       <c r="X6" s="2">
-        <v>0.905660377358491</v>
+        <v>0.90566037735849103</v>
       </c>
       <c r="Y6" s="2">
-        <v>5.1880358598207</v>
+        <v>5.1880358598207001</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.906308068459658</v>
+        <v>0.90630806845965795</v>
       </c>
       <c r="AA6" s="4">
-        <v>8.16461137250319E-5</v>
+        <v>8.1646113725031898E-5</v>
       </c>
       <c r="AB6" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="AC6" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B7" s="2">
-        <v>4.91094420600858</v>
+        <v>4.9109442060085797</v>
       </c>
       <c r="C7" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D7" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2">
-        <v>0.999605055292259</v>
+        <v>0.99960505529225896</v>
       </c>
       <c r="H7" s="2">
-        <v>0.995708154506437</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>63</v>
+        <v>0.99570815450643702</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
       </c>
       <c r="J7" s="2">
-        <v>0.723404255319149</v>
+        <v>0.72340425531914898</v>
       </c>
       <c r="K7" s="2">
-        <v>3.42060085836909</v>
+        <v>3.4206008583690899</v>
       </c>
       <c r="L7" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>0</v>
       </c>
       <c r="N7" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O7" s="2">
-        <v>0.00429184549356223</v>
+        <v>4.29184549356223E-3</v>
       </c>
       <c r="P7" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.998927038626609</v>
+        <v>0.99892703862660903</v>
       </c>
       <c r="R7" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S7" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="T7" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="U7" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="V7" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="W7" s="2">
-        <v>3.93552875695732</v>
+        <v>3.9355287569573201</v>
       </c>
       <c r="X7" s="2">
-        <v>0.991683991683991</v>
+        <v>0.99168399168399102</v>
       </c>
       <c r="Y7" s="2">
-        <v>0.00107296137339055</v>
+        <v>1.0729613733905499E-3</v>
       </c>
       <c r="Z7" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="2">
-        <v>0.00120336943441636</v>
+        <v>1.20336943441636E-3</v>
       </c>
       <c r="AB7" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="AC7" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
         <v>59</v>
       </c>
       <c r="B8" s="2">
-        <v>1.99904973075704</v>
+        <v>1.9990497307570401</v>
       </c>
       <c r="C8" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D8" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G8" s="2">
-        <v>0.998533724340176</v>
+        <v>0.99853372434017595</v>
       </c>
       <c r="H8" s="2">
-        <v>0.999049730757047</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>63</v>
+        <v>0.99904973075704695</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
       </c>
       <c r="J8" s="2">
-        <v>0.402752293577981</v>
+        <v>0.40275229357798098</v>
       </c>
       <c r="K8" s="2">
-        <v>0.0570161545771301</v>
+        <v>5.70161545771301E-2</v>
       </c>
       <c r="L8" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="b">
         <v>0</v>
       </c>
       <c r="N8" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O8" s="2">
-        <v>9.50269242952169E-4</v>
+        <v>9.5026924295216902E-4</v>
       </c>
       <c r="P8" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R8" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S8" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="T8" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="U8" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="V8" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="W8" s="2">
-        <v>5.10447761194029</v>
+        <v>5.1044776119402897</v>
       </c>
       <c r="X8" s="2">
-        <v>0.999023755287992</v>
+        <v>0.99902375528799203</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="2">
-        <v>2.80839710735097E-4</v>
+        <v>2.8083971073509698E-4</v>
       </c>
       <c r="AB8" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="AC8" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
         <v>60</v>
       </c>
       <c r="B9" s="2">
-        <v>2.63459051724137</v>
+        <v>2.6345905172413699</v>
       </c>
       <c r="C9" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D9" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G9" s="2">
-        <v>0.908477889078915</v>
+        <v>0.90847788907891502</v>
       </c>
       <c r="H9" s="2">
-        <v>0.999353448275862</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>63</v>
+        <v>0.99935344827586203</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
       </c>
       <c r="J9" s="2">
-        <v>0.645562173689241</v>
+        <v>0.64556217368924096</v>
       </c>
       <c r="K9" s="2">
-        <v>0.9875</v>
+        <v>0.98750000000000004</v>
       </c>
       <c r="L9" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="b">
         <v>0</v>
       </c>
       <c r="N9" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O9" s="2">
-        <v>6.46551724137931E-4</v>
+        <v>6.4655172413793103E-4</v>
       </c>
       <c r="P9" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R9" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S9" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="T9" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="U9" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="W9" s="2">
         <v>4.01500636801594</v>
       </c>
       <c r="X9" s="2">
-        <v>0.999329908420817</v>
+        <v>0.99932990842081704</v>
       </c>
       <c r="Y9" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="2">
-        <v>1.92246074975969E-4</v>
+        <v>1.9224607497596901E-4</v>
       </c>
       <c r="AB9" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="AC9" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
         <v>61</v>
       </c>
       <c r="B10" s="2">
-        <v>4.01502471933257</v>
+        <v>4.0150247193325699</v>
       </c>
       <c r="C10" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D10" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2">
-        <v>0.987113833527212</v>
+        <v>0.98711383352721205</v>
       </c>
       <c r="H10" s="2">
-        <v>0.999774693583273</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>63</v>
+        <v>0.99977469358327298</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
       </c>
       <c r="J10" s="2">
-        <v>0.0239059210444358</v>
+        <v>2.3905921044435799E-2</v>
       </c>
       <c r="K10" s="2">
-        <v>2.51812751055721</v>
+        <v>2.5181275105572101</v>
       </c>
       <c r="L10" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="b">
         <v>0</v>
       </c>
       <c r="N10" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O10" s="2">
-        <v>2.25306416726748E-4</v>
+        <v>2.2530641672674801E-4</v>
       </c>
       <c r="P10" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="2">
-        <v>0.999987125347615</v>
+        <v>0.99998712534761502</v>
       </c>
       <c r="R10" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S10" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="T10" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="U10" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="W10" s="2">
-        <v>7.89907352651291</v>
+        <v>7.8990735265129102</v>
       </c>
       <c r="X10" s="2">
-        <v>0.999922087028788</v>
+        <v>0.99992208702878804</v>
       </c>
       <c r="Y10" s="4">
-        <v>1.28746523843856E-5</v>
+        <v>1.2874652384385601E-5</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="AA10" s="4">
         <v>1.20830975944685E-5</v>
       </c>
       <c r="AB10" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="AC10" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
         <v>62</v>
       </c>
       <c r="B11" s="2">
-        <v>3.8715036338351</v>
+        <v>3.8715036338351001</v>
       </c>
       <c r="C11" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D11" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G11" s="2">
-        <v>0.98829128948845</v>
+        <v>0.98829128948845002</v>
       </c>
       <c r="H11" s="2">
-        <v>0.999778885934236</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>63</v>
+        <v>0.99977888593423603</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
       </c>
       <c r="J11" s="2">
-        <v>0.0756529602638438</v>
+        <v>7.5652960263843799E-2</v>
       </c>
       <c r="K11" s="2">
-        <v>2.35013994192846</v>
+        <v>2.3501399419284601</v>
       </c>
       <c r="L11" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="b">
         <v>0</v>
       </c>
       <c r="N11" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O11" s="2">
-        <v>2.21114065763978E-4</v>
+        <v>2.2111406576397799E-4</v>
       </c>
       <c r="P11" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="2">
-        <v>0.999982543626387</v>
+        <v>0.99998254362638705</v>
       </c>
       <c r="R11" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S11" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="T11" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="U11" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="W11" s="2">
-        <v>7.62170332126413</v>
+        <v>7.6217033212641301</v>
       </c>
       <c r="X11" s="2">
-        <v>0.999929410934246</v>
+        <v>0.99992941093424603</v>
       </c>
       <c r="Y11" s="4">
-        <v>1.74563736129456E-5</v>
+        <v>1.7456373612945601E-5</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="AA11" s="4">
         <v>1.56093601528156E-5</v>
       </c>
       <c r="AB11" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="AC11" s="2" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/evaluation/bgw-monarch-summary-data/OriginalGraphs.xlsx
+++ b/evaluation/bgw-monarch-summary-data/OriginalGraphs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jesualdo/Documents/GitHub/oquare-kg/evaluation/bgw-monarch-summary-data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jesualdo/git/oquare-kg/evaluation/bgw-monarch-summary-data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABAD1EAA-69DB-4A47-9419-B856B9547DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAD59529-C597-CC4A-A689-3ED9D4347910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="44800" windowHeight="22800" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17380" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characteristics" sheetId="1" r:id="rId1"/>
@@ -37,181 +37,181 @@
     <t>Structural accuracy</t>
   </si>
   <si>
+    <t>Consistency</t>
+  </si>
+  <si>
+    <t>Syntactic validity</t>
+  </si>
+  <si>
+    <t>Redundancy</t>
+  </si>
+  <si>
+    <t>Interpretability</t>
+  </si>
+  <si>
+    <t>Inference</t>
+  </si>
+  <si>
+    <t>Understandability</t>
+  </si>
+  <si>
+    <t>Trustworthiness</t>
+  </si>
+  <si>
+    <t>Provenance</t>
+  </si>
+  <si>
+    <t>Clustering</t>
+  </si>
+  <si>
+    <t>Interoperability</t>
+  </si>
+  <si>
     <t>Annotation richness metric</t>
   </si>
   <si>
-    <t>Consistency</t>
+    <t>Versatility</t>
   </si>
   <si>
     <t>Basic provenance metric</t>
   </si>
   <si>
-    <t>Syntactic validity</t>
-  </si>
-  <si>
     <t>Classes per instance metric</t>
   </si>
   <si>
-    <t>Redundancy</t>
+    <t>Licensing</t>
   </si>
   <si>
     <t>Compatible datatype metric</t>
   </si>
   <si>
+    <t>Accessibility</t>
+  </si>
+  <si>
     <t>Structural</t>
   </si>
   <si>
-    <t>Interpretability</t>
-  </si>
-  <si>
     <t>Deprecated terms metric</t>
   </si>
   <si>
     <t>Functional adequacy</t>
   </si>
   <si>
-    <t>Inference</t>
+    <t>Reusability</t>
   </si>
   <si>
     <t>Dereferenceable uris metric</t>
   </si>
   <si>
-    <t>Understandability</t>
-  </si>
-  <si>
     <t>Compatibility</t>
   </si>
   <si>
+    <t>Transferability</t>
+  </si>
+  <si>
     <t>Descriptions per instance metric</t>
   </si>
   <si>
-    <t>Trustworthiness</t>
+    <t>Operability</t>
+  </si>
+  <si>
+    <t>Reliability</t>
   </si>
   <si>
     <t>Different serialisation formats metric</t>
   </si>
   <si>
-    <t>Transferability</t>
-  </si>
-  <si>
-    <t>Provenance</t>
+    <t>Maintainability</t>
+  </si>
+  <si>
+    <t>crm2tfac</t>
   </si>
   <si>
     <t>Entities with no type metric</t>
   </si>
   <si>
-    <t>Clustering</t>
-  </si>
-  <si>
-    <t>Operability</t>
-  </si>
-  <si>
     <t>Evidence metric</t>
   </si>
   <si>
-    <t>Reliability</t>
-  </si>
-  <si>
     <t>Extensional conciseness metric</t>
   </si>
   <si>
-    <t>Interoperability</t>
-  </si>
-  <si>
-    <t>Maintainability</t>
-  </si>
-  <si>
     <t>Human readable license metric</t>
   </si>
   <si>
-    <t>Versatility</t>
+    <t>Instances with multiple types metric</t>
+  </si>
+  <si>
+    <t>Instances with no description metric</t>
+  </si>
+  <si>
+    <t>Instances with no name metric</t>
+  </si>
+  <si>
+    <t>crm2phen</t>
+  </si>
+  <si>
+    <t>Instances with no synonyms metric</t>
+  </si>
+  <si>
+    <t>Machine license metric</t>
+  </si>
+  <si>
+    <t>Misplaced class property metric</t>
+  </si>
+  <si>
+    <t>Misused properties metric</t>
+  </si>
+  <si>
+    <t>crm2gene</t>
+  </si>
+  <si>
+    <t>Multiple languages metric</t>
+  </si>
+  <si>
+    <t>Names per instance metric</t>
+  </si>
+  <si>
+    <t>crm</t>
+  </si>
+  <si>
+    <t>Relations per node metric</t>
+  </si>
+  <si>
+    <t>Reuse terms metric</t>
+  </si>
+  <si>
+    <t>Synonyms per instance metric</t>
+  </si>
+  <si>
+    <t>all</t>
+  </si>
+  <si>
+    <t>Traceability of the data metric</t>
+  </si>
+  <si>
+    <t>Usage of undefined terms metric</t>
   </si>
   <si>
     <t>assoc</t>
   </si>
   <si>
-    <t>Licensing</t>
-  </si>
-  <si>
-    <t>Instances with multiple types metric</t>
-  </si>
-  <si>
-    <t>Accessibility</t>
-  </si>
-  <si>
-    <t>Instances with no description metric</t>
-  </si>
-  <si>
-    <t>Instances with no name metric</t>
-  </si>
-  <si>
-    <t>Reusability</t>
-  </si>
-  <si>
-    <t>Instances with no synonyms metric</t>
-  </si>
-  <si>
-    <t>Machine license metric</t>
+    <t>Used vocabularies metric</t>
+  </si>
+  <si>
+    <t>Valid format metric</t>
   </si>
   <si>
     <t>pheno</t>
   </si>
   <si>
-    <t>Misplaced class property metric</t>
-  </si>
-  <si>
-    <t>Misused properties metric</t>
-  </si>
-  <si>
-    <t>Multiple languages metric</t>
-  </si>
-  <si>
-    <t>Names per instance metric</t>
-  </si>
-  <si>
-    <t>Relations per node metric</t>
-  </si>
-  <si>
     <t>gene_pheno_nervous</t>
   </si>
   <si>
-    <t>Reuse terms metric</t>
-  </si>
-  <si>
-    <t>Synonyms per instance metric</t>
-  </si>
-  <si>
-    <t>Traceability of the data metric</t>
-  </si>
-  <si>
     <t>gene_pheno_human</t>
   </si>
   <si>
-    <t>Usage of undefined terms metric</t>
-  </si>
-  <si>
-    <t>Used vocabularies metric</t>
-  </si>
-  <si>
-    <t>Valid format metric</t>
-  </si>
-  <si>
     <t>complete</t>
-  </si>
-  <si>
-    <t>crm2tfac</t>
-  </si>
-  <si>
-    <t>crm2phen</t>
-  </si>
-  <si>
-    <t>crm2gene</t>
-  </si>
-  <si>
-    <t>crm</t>
-  </si>
-  <si>
-    <t>all</t>
   </si>
 </sst>
 </file>
@@ -491,36 +491,36 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" s="2">
-        <v>4.0539682539682502</v>
+        <v>3.7111111111111099</v>
       </c>
       <c r="C2" s="2">
-        <v>3.61666666666666</v>
+        <v>2.7933333333333299</v>
       </c>
       <c r="D2" s="2">
         <v>3</v>
@@ -532,21 +532,21 @@
         <v>1</v>
       </c>
       <c r="G2" s="2">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="H2" s="2">
-        <v>2.3333333333333299</v>
+        <v>1.6666666666666601</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B3" s="2">
         <v>3.7682539682539602</v>
       </c>
       <c r="C3" s="2">
-        <v>3.11666666666666</v>
+        <v>2.1916666666666602</v>
       </c>
       <c r="D3" s="2">
         <v>3</v>
@@ -558,21 +558,21 @@
         <v>1</v>
       </c>
       <c r="G3" s="2">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="H3" s="2">
-        <v>2.3333333333333299</v>
+        <v>1.6666666666666601</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B4" s="2">
-        <v>3.9396825396825399</v>
+        <v>3.7111111111111099</v>
       </c>
       <c r="C4" s="2">
-        <v>3.7616666666666601</v>
+        <v>2.21</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
@@ -584,21 +584,21 @@
         <v>1</v>
       </c>
       <c r="G4" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4" s="2">
-        <v>2.3333333333333299</v>
+        <v>1.6666666666666601</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2">
-        <v>3.9396825396825399</v>
+        <v>3.8825396825396798</v>
       </c>
       <c r="C5" s="2">
-        <v>3.7366666666666601</v>
+        <v>2.78833333333333</v>
       </c>
       <c r="D5" s="2">
         <v>3</v>
@@ -610,21 +610,21 @@
         <v>1</v>
       </c>
       <c r="G5" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" s="2">
-        <v>2.3333333333333299</v>
+        <v>1.6666666666666601</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B6" s="2">
-        <v>3.9396825396825399</v>
+        <v>3.8825396825396798</v>
       </c>
       <c r="C6" s="2">
-        <v>3.7450000000000001</v>
+        <v>2.78833333333333</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -636,21 +636,21 @@
         <v>1</v>
       </c>
       <c r="G6" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H6" s="2">
-        <v>2.3333333333333299</v>
+        <v>1.6666666666666601</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>3.7111111111111099</v>
+        <v>4.0539682539682502</v>
       </c>
       <c r="C7" s="2">
-        <v>2.7933333333333299</v>
+        <v>3.5666666666666602</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
@@ -662,10 +662,10 @@
         <v>1</v>
       </c>
       <c r="G7" s="2">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="H7" s="2">
-        <v>1.6666666666666601</v>
+        <v>2.3333333333333299</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -676,7 +676,7 @@
         <v>3.7682539682539602</v>
       </c>
       <c r="C8" s="2">
-        <v>2.1916666666666602</v>
+        <v>3.0166666666666599</v>
       </c>
       <c r="D8" s="2">
         <v>3</v>
@@ -688,10 +688,10 @@
         <v>1</v>
       </c>
       <c r="G8" s="2">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="H8" s="2">
-        <v>1.6666666666666601</v>
+        <v>2.3333333333333299</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -699,10 +699,10 @@
         <v>60</v>
       </c>
       <c r="B9" s="2">
-        <v>3.7111111111111099</v>
+        <v>3.9396825396825399</v>
       </c>
       <c r="C9" s="2">
-        <v>2.21</v>
+        <v>3.7616666666666601</v>
       </c>
       <c r="D9" s="2">
         <v>3</v>
@@ -714,10 +714,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" s="2">
-        <v>1.6666666666666601</v>
+        <v>2.3333333333333299</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -725,10 +725,10 @@
         <v>61</v>
       </c>
       <c r="B10" s="2">
-        <v>3.8825396825396798</v>
+        <v>3.9396825396825399</v>
       </c>
       <c r="C10" s="2">
-        <v>2.78833333333333</v>
+        <v>3.7366666666666601</v>
       </c>
       <c r="D10" s="2">
         <v>3</v>
@@ -740,10 +740,10 @@
         <v>1</v>
       </c>
       <c r="G10" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" s="2">
-        <v>1.6666666666666601</v>
+        <v>2.3333333333333299</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -751,10 +751,10 @@
         <v>62</v>
       </c>
       <c r="B11" s="2">
-        <v>3.8825396825396798</v>
+        <v>3.9396825396825399</v>
       </c>
       <c r="C11" s="2">
-        <v>2.78833333333333</v>
+        <v>3.7450000000000001</v>
       </c>
       <c r="D11" s="2">
         <v>3</v>
@@ -766,10 +766,10 @@
         <v>1</v>
       </c>
       <c r="G11" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" s="2">
-        <v>1.6666666666666601</v>
+        <v>2.3333333333333299</v>
       </c>
     </row>
   </sheetData>
@@ -796,51 +796,51 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="M1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="O1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="Q1" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
@@ -849,7 +849,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="3">
-        <v>4.8571428571428497</v>
+        <v>4</v>
       </c>
       <c r="E2" s="3">
         <v>3.6666666666666599</v>
@@ -858,22 +858,22 @@
         <v>5</v>
       </c>
       <c r="G2" s="3">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="H2" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="I2" s="3">
         <v>4</v>
       </c>
-      <c r="I2" s="3">
-        <v>2.75</v>
-      </c>
       <c r="J2" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K2" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2" s="3">
-        <v>4.3333333333333304</v>
+        <v>3.1666666666666599</v>
       </c>
       <c r="M2" s="3">
         <v>3</v>
@@ -885,15 +885,15 @@
         <v>1</v>
       </c>
       <c r="P2" s="3">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Q2" s="3">
-        <v>2.3333333333333299</v>
+        <v>1.6666666666666601</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B3" s="3">
         <v>1</v>
@@ -917,16 +917,16 @@
         <v>3</v>
       </c>
       <c r="I3" s="3">
-        <v>2.25</v>
+        <v>3.125</v>
       </c>
       <c r="J3" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K3" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L3" s="3">
-        <v>3.3333333333333299</v>
+        <v>2.8333333333333299</v>
       </c>
       <c r="M3" s="3">
         <v>3</v>
@@ -938,15 +938,15 @@
         <v>1</v>
       </c>
       <c r="P3" s="3">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="Q3" s="3">
-        <v>2.3333333333333299</v>
+        <v>1.6666666666666601</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B4" s="3">
         <v>1</v>
@@ -955,7 +955,7 @@
         <v>5</v>
       </c>
       <c r="D4" s="3">
-        <v>4.5714285714285703</v>
+        <v>4</v>
       </c>
       <c r="E4" s="3">
         <v>3.6666666666666599</v>
@@ -964,22 +964,22 @@
         <v>5</v>
       </c>
       <c r="G4" s="3">
-        <v>4.4000000000000004</v>
+        <v>3.6</v>
       </c>
       <c r="H4" s="3">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="I4" s="3">
-        <v>4.375</v>
+        <v>3.25</v>
       </c>
       <c r="J4" s="3">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="K4" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L4" s="3">
-        <v>3.8333333333333299</v>
+        <v>2.5</v>
       </c>
       <c r="M4" s="3">
         <v>3</v>
@@ -991,15 +991,15 @@
         <v>1</v>
       </c>
       <c r="P4" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q4" s="3">
-        <v>2.3333333333333299</v>
+        <v>1.6666666666666601</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1008,7 +1008,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="3">
-        <v>4.5714285714285703</v>
+        <v>4.4285714285714199</v>
       </c>
       <c r="E5" s="3">
         <v>3.6666666666666599</v>
@@ -1017,22 +1017,22 @@
         <v>5</v>
       </c>
       <c r="G5" s="3">
-        <v>4.4000000000000004</v>
+        <v>4.2</v>
       </c>
       <c r="H5" s="3">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="I5" s="3">
-        <v>4.25</v>
+        <v>3.375</v>
       </c>
       <c r="J5" s="3">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="K5" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L5" s="3">
-        <v>3.8333333333333299</v>
+        <v>3.6666666666666599</v>
       </c>
       <c r="M5" s="3">
         <v>3</v>
@@ -1044,15 +1044,15 @@
         <v>1</v>
       </c>
       <c r="P5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q5" s="3">
-        <v>2.3333333333333299</v>
+        <v>1.6666666666666601</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1061,7 +1061,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="3">
-        <v>4.5714285714285703</v>
+        <v>4.4285714285714199</v>
       </c>
       <c r="E6" s="3">
         <v>3.6666666666666599</v>
@@ -1070,22 +1070,22 @@
         <v>5</v>
       </c>
       <c r="G6" s="3">
-        <v>4.4000000000000004</v>
+        <v>4.2</v>
       </c>
       <c r="H6" s="3">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="I6" s="3">
-        <v>4.125</v>
+        <v>3.375</v>
       </c>
       <c r="J6" s="3">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="K6" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6" s="3">
-        <v>4</v>
+        <v>3.6666666666666599</v>
       </c>
       <c r="M6" s="3">
         <v>3</v>
@@ -1097,15 +1097,15 @@
         <v>1</v>
       </c>
       <c r="P6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q6" s="3">
-        <v>2.3333333333333299</v>
+        <v>1.6666666666666601</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1114,7 +1114,7 @@
         <v>5</v>
       </c>
       <c r="D7" s="3">
-        <v>4</v>
+        <v>4.8571428571428497</v>
       </c>
       <c r="E7" s="3">
         <v>3.6666666666666599</v>
@@ -1123,22 +1123,22 @@
         <v>5</v>
       </c>
       <c r="G7" s="3">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="H7" s="3">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="I7" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="J7" s="3">
         <v>4</v>
       </c>
-      <c r="J7" s="3">
-        <v>3</v>
-      </c>
       <c r="K7" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L7" s="3">
-        <v>3.1666666666666599</v>
+        <v>4.3333333333333304</v>
       </c>
       <c r="M7" s="3">
         <v>3</v>
@@ -1150,10 +1150,10 @@
         <v>1</v>
       </c>
       <c r="P7" s="3">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" s="3">
-        <v>1.6666666666666601</v>
+        <v>2.3333333333333299</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1182,16 +1182,16 @@
         <v>3</v>
       </c>
       <c r="I8" s="3">
-        <v>3.125</v>
+        <v>1.75</v>
       </c>
       <c r="J8" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K8" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L8" s="3">
-        <v>2.8333333333333299</v>
+        <v>3.3333333333333299</v>
       </c>
       <c r="M8" s="3">
         <v>3</v>
@@ -1203,10 +1203,10 @@
         <v>1</v>
       </c>
       <c r="P8" s="3">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q8" s="3">
-        <v>1.6666666666666601</v>
+        <v>2.3333333333333299</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1220,7 +1220,7 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>4</v>
+        <v>4.5714285714285703</v>
       </c>
       <c r="E9" s="3">
         <v>3.6666666666666599</v>
@@ -1229,22 +1229,22 @@
         <v>5</v>
       </c>
       <c r="G9" s="3">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H9" s="3">
         <v>3.6</v>
       </c>
-      <c r="H9" s="3">
-        <v>2.8</v>
-      </c>
       <c r="I9" s="3">
-        <v>3.25</v>
+        <v>4.375</v>
       </c>
       <c r="J9" s="3">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="K9" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L9" s="3">
-        <v>2.5</v>
+        <v>3.8333333333333299</v>
       </c>
       <c r="M9" s="3">
         <v>3</v>
@@ -1256,116 +1256,116 @@
         <v>1</v>
       </c>
       <c r="P9" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q9" s="3">
-        <v>1.6666666666666601</v>
+        <v>2.3333333333333299</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="3">
-        <v>1</v>
-      </c>
-      <c r="C10" s="3">
-        <v>5</v>
-      </c>
-      <c r="D10" s="3">
-        <v>4.4285714285714199</v>
-      </c>
-      <c r="E10" s="3">
+      <c r="B10" s="2">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2">
+        <v>5</v>
+      </c>
+      <c r="D10" s="2">
+        <v>4.5714285714285703</v>
+      </c>
+      <c r="E10" s="2">
         <v>3.6666666666666599</v>
       </c>
-      <c r="F10" s="3">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3">
-        <v>4.2</v>
-      </c>
-      <c r="H10" s="3">
-        <v>3.4</v>
-      </c>
-      <c r="I10" s="3">
-        <v>3.375</v>
-      </c>
-      <c r="J10" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="K10" s="3">
-        <v>1</v>
-      </c>
-      <c r="L10" s="3">
+      <c r="F10" s="2">
+        <v>5</v>
+      </c>
+      <c r="G10" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H10" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="I10" s="2">
+        <v>4.25</v>
+      </c>
+      <c r="J10" s="2">
+        <v>4</v>
+      </c>
+      <c r="K10" s="2">
+        <v>3</v>
+      </c>
+      <c r="L10" s="2">
+        <v>3.8333333333333299</v>
+      </c>
+      <c r="M10" s="2">
+        <v>3</v>
+      </c>
+      <c r="N10" s="2">
+        <v>1</v>
+      </c>
+      <c r="O10" s="2">
+        <v>1</v>
+      </c>
+      <c r="P10" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>2.3333333333333299</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2">
+        <v>5</v>
+      </c>
+      <c r="D11" s="2">
+        <v>4.5714285714285703</v>
+      </c>
+      <c r="E11" s="2">
         <v>3.6666666666666599</v>
       </c>
-      <c r="M10" s="3">
-        <v>3</v>
-      </c>
-      <c r="N10" s="3">
-        <v>1</v>
-      </c>
-      <c r="O10" s="3">
-        <v>1</v>
-      </c>
-      <c r="P10" s="3">
-        <v>2</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>1.6666666666666601</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B11" s="3">
-        <v>1</v>
-      </c>
-      <c r="C11" s="3">
-        <v>5</v>
-      </c>
-      <c r="D11" s="3">
-        <v>4.4285714285714199</v>
-      </c>
-      <c r="E11" s="3">
-        <v>3.6666666666666599</v>
-      </c>
-      <c r="F11" s="3">
-        <v>5</v>
-      </c>
-      <c r="G11" s="3">
-        <v>4.2</v>
-      </c>
-      <c r="H11" s="3">
-        <v>3.4</v>
-      </c>
-      <c r="I11" s="3">
-        <v>3.375</v>
-      </c>
-      <c r="J11" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="K11" s="3">
-        <v>1</v>
-      </c>
-      <c r="L11" s="3">
-        <v>3.6666666666666599</v>
-      </c>
-      <c r="M11" s="3">
-        <v>3</v>
-      </c>
-      <c r="N11" s="3">
-        <v>1</v>
-      </c>
-      <c r="O11" s="3">
-        <v>1</v>
-      </c>
-      <c r="P11" s="3">
-        <v>2</v>
-      </c>
-      <c r="Q11" s="3">
-        <v>1.6666666666666601</v>
+      <c r="F11" s="2">
+        <v>5</v>
+      </c>
+      <c r="G11" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H11" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="I11" s="2">
+        <v>4.125</v>
+      </c>
+      <c r="J11" s="2">
+        <v>4</v>
+      </c>
+      <c r="K11" s="2">
+        <v>3</v>
+      </c>
+      <c r="L11" s="2">
+        <v>4</v>
+      </c>
+      <c r="M11" s="2">
+        <v>3</v>
+      </c>
+      <c r="N11" s="2">
+        <v>1</v>
+      </c>
+      <c r="O11" s="2">
+        <v>1</v>
+      </c>
+      <c r="P11" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>2.3333333333333299</v>
       </c>
     </row>
   </sheetData>
@@ -1386,58 +1386,58 @@
   <sheetData>
     <row r="1" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S1" s="2" t="s">
         <v>44</v>
@@ -1446,36 +1446,36 @@
         <v>45</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W1" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Y1" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Z1" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AA1" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AB1" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AC1" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" s="2">
         <v>5</v>
@@ -1484,7 +1484,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E2" s="2">
         <v>5</v>
@@ -1493,19 +1493,19 @@
         <v>5</v>
       </c>
       <c r="G2" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H2" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2" s="2">
         <v>1</v>
       </c>
       <c r="J2" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K2" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L2" s="2">
         <v>5</v>
@@ -1514,16 +1514,16 @@
         <v>1</v>
       </c>
       <c r="N2" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O2" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P2" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q2" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R2" s="2">
         <v>1</v>
@@ -1541,16 +1541,16 @@
         <v>5</v>
       </c>
       <c r="W2" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="X2" s="2">
         <v>5</v>
       </c>
       <c r="Y2" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z2" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA2" s="2">
         <v>5</v>
@@ -1564,16 +1564,16 @@
     </row>
     <row r="3" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B3" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3" s="2">
         <v>5</v>
@@ -1582,56 +1582,56 @@
         <v>5</v>
       </c>
       <c r="G3" s="2">
+        <v>5</v>
+      </c>
+      <c r="H3" s="2">
+        <v>5</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2">
+        <v>3</v>
+      </c>
+      <c r="K3" s="2">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2">
+        <v>5</v>
+      </c>
+      <c r="M3" s="2">
+        <v>1</v>
+      </c>
+      <c r="N3" s="2">
+        <v>3</v>
+      </c>
+      <c r="O3" s="2">
+        <v>5</v>
+      </c>
+      <c r="P3" s="2">
+        <v>5</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>1</v>
+      </c>
+      <c r="R3" s="2">
+        <v>1</v>
+      </c>
+      <c r="S3" s="2">
+        <v>5</v>
+      </c>
+      <c r="T3" s="2">
+        <v>5</v>
+      </c>
+      <c r="U3" s="2">
+        <v>1</v>
+      </c>
+      <c r="V3" s="2">
+        <v>5</v>
+      </c>
+      <c r="W3" s="2">
         <v>2</v>
       </c>
-      <c r="H3" s="2">
-        <v>3</v>
-      </c>
-      <c r="I3" s="2">
-        <v>1</v>
-      </c>
-      <c r="J3" s="2">
-        <v>5</v>
-      </c>
-      <c r="K3" s="2">
-        <v>3</v>
-      </c>
-      <c r="L3" s="2">
-        <v>5</v>
-      </c>
-      <c r="M3" s="2">
-        <v>1</v>
-      </c>
-      <c r="N3" s="2">
-        <v>3</v>
-      </c>
-      <c r="O3" s="2">
-        <v>2</v>
-      </c>
-      <c r="P3" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q3" s="2">
-        <v>2</v>
-      </c>
-      <c r="R3" s="2">
-        <v>1</v>
-      </c>
-      <c r="S3" s="2">
-        <v>5</v>
-      </c>
-      <c r="T3" s="2">
-        <v>5</v>
-      </c>
-      <c r="U3" s="2">
-        <v>1</v>
-      </c>
-      <c r="V3" s="2">
-        <v>2</v>
-      </c>
-      <c r="W3" s="2">
-        <v>5</v>
-      </c>
       <c r="X3" s="2">
         <v>5</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>1</v>
       </c>
       <c r="Z3" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA3" s="2">
         <v>5</v>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="4" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B4" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4" s="2">
         <v>1</v>
@@ -1680,10 +1680,10 @@
         <v>1</v>
       </c>
       <c r="J4" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K4" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L4" s="2">
         <v>5</v>
@@ -1692,16 +1692,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O4" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P4" s="2">
         <v>5</v>
       </c>
       <c r="Q4" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R4" s="2">
         <v>1</v>
@@ -1725,10 +1725,10 @@
         <v>5</v>
       </c>
       <c r="Y4" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z4" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA4" s="2">
         <v>5</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="5" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" s="2">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>5</v>
       </c>
       <c r="K5" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5" s="2">
         <v>5</v>
@@ -1781,16 +1781,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O5" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P5" s="2">
         <v>5</v>
       </c>
       <c r="Q5" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R5" s="2">
         <v>1</v>
@@ -1808,16 +1808,16 @@
         <v>5</v>
       </c>
       <c r="W5" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="X5" s="2">
         <v>5</v>
       </c>
       <c r="Y5" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z5" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA5" s="2">
         <v>5</v>
@@ -1831,10 +1831,10 @@
     </row>
     <row r="6" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B6" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" s="2">
         <v>1</v>
@@ -1861,7 +1861,7 @@
         <v>5</v>
       </c>
       <c r="K6" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L6" s="2">
         <v>5</v>
@@ -1870,16 +1870,16 @@
         <v>1</v>
       </c>
       <c r="N6" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O6" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P6" s="2">
         <v>5</v>
       </c>
       <c r="Q6" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R6" s="2">
         <v>1</v>
@@ -1897,16 +1897,16 @@
         <v>5</v>
       </c>
       <c r="W6" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="X6" s="2">
         <v>5</v>
       </c>
       <c r="Y6" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z6" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA6" s="2">
         <v>5</v>
@@ -1920,16 +1920,16 @@
     </row>
     <row r="7" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C7" s="2">
         <v>1</v>
       </c>
       <c r="D7" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E7" s="2">
         <v>5</v>
@@ -1938,19 +1938,19 @@
         <v>5</v>
       </c>
       <c r="G7" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H7" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I7" s="2">
         <v>1</v>
       </c>
       <c r="J7" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K7" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L7" s="2">
         <v>5</v>
@@ -1959,16 +1959,16 @@
         <v>1</v>
       </c>
       <c r="N7" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O7" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P7" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q7" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R7" s="2">
         <v>1</v>
@@ -1986,16 +1986,16 @@
         <v>5</v>
       </c>
       <c r="W7" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X7" s="2">
         <v>5</v>
       </c>
       <c r="Y7" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z7" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA7" s="2">
         <v>5</v>
@@ -2012,34 +2012,34 @@
         <v>59</v>
       </c>
       <c r="B8" s="2">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
+        <v>5</v>
+      </c>
+      <c r="F8" s="2">
+        <v>5</v>
+      </c>
+      <c r="G8" s="2">
         <v>2</v>
       </c>
-      <c r="C8" s="2">
-        <v>1</v>
-      </c>
-      <c r="D8" s="2">
-        <v>3</v>
-      </c>
-      <c r="E8" s="2">
-        <v>5</v>
-      </c>
-      <c r="F8" s="2">
-        <v>5</v>
-      </c>
-      <c r="G8" s="2">
-        <v>5</v>
-      </c>
       <c r="H8" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I8" s="2">
         <v>1</v>
       </c>
       <c r="J8" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K8" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L8" s="2">
         <v>5</v>
@@ -2051,13 +2051,13 @@
         <v>3</v>
       </c>
       <c r="O8" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P8" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q8" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8" s="2">
         <v>1</v>
@@ -2072,10 +2072,10 @@
         <v>1</v>
       </c>
       <c r="V8" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W8" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="X8" s="2">
         <v>5</v>
@@ -2084,7 +2084,7 @@
         <v>1</v>
       </c>
       <c r="Z8" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA8" s="2">
         <v>5</v>
@@ -2101,7 +2101,7 @@
         <v>60</v>
       </c>
       <c r="B9" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" s="2">
         <v>1</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="J9" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K9" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L9" s="2">
         <v>5</v>
@@ -2137,16 +2137,16 @@
         <v>1</v>
       </c>
       <c r="N9" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O9" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P9" s="2">
         <v>5</v>
       </c>
       <c r="Q9" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R9" s="2">
         <v>1</v>
@@ -2170,10 +2170,10 @@
         <v>5</v>
       </c>
       <c r="Y9" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z9" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA9" s="2">
         <v>5</v>
@@ -2190,52 +2190,52 @@
         <v>61</v>
       </c>
       <c r="B10" s="2">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2">
+        <v>3</v>
+      </c>
+      <c r="E10" s="2">
+        <v>5</v>
+      </c>
+      <c r="F10" s="2">
+        <v>5</v>
+      </c>
+      <c r="G10" s="2">
+        <v>5</v>
+      </c>
+      <c r="H10" s="2">
+        <v>5</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2">
+        <v>5</v>
+      </c>
+      <c r="K10" s="2">
+        <v>3</v>
+      </c>
+      <c r="L10" s="2">
+        <v>5</v>
+      </c>
+      <c r="M10" s="2">
+        <v>1</v>
+      </c>
+      <c r="N10" s="2">
         <v>4</v>
       </c>
-      <c r="C10" s="2">
-        <v>1</v>
-      </c>
-      <c r="D10" s="2">
-        <v>3</v>
-      </c>
-      <c r="E10" s="2">
-        <v>5</v>
-      </c>
-      <c r="F10" s="2">
-        <v>5</v>
-      </c>
-      <c r="G10" s="2">
-        <v>5</v>
-      </c>
-      <c r="H10" s="2">
-        <v>5</v>
-      </c>
-      <c r="I10" s="2">
-        <v>1</v>
-      </c>
-      <c r="J10" s="2">
-        <v>5</v>
-      </c>
-      <c r="K10" s="2">
+      <c r="O10" s="2">
         <v>4</v>
       </c>
-      <c r="L10" s="2">
-        <v>5</v>
-      </c>
-      <c r="M10" s="2">
-        <v>1</v>
-      </c>
-      <c r="N10" s="2">
-        <v>3</v>
-      </c>
-      <c r="O10" s="2">
-        <v>5</v>
-      </c>
       <c r="P10" s="2">
         <v>5</v>
       </c>
       <c r="Q10" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R10" s="2">
         <v>1</v>
@@ -2253,16 +2253,16 @@
         <v>5</v>
       </c>
       <c r="W10" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="X10" s="2">
         <v>5</v>
       </c>
       <c r="Y10" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z10" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA10" s="2">
         <v>5</v>
@@ -2279,53 +2279,53 @@
         <v>62</v>
       </c>
       <c r="B11" s="2">
+        <v>5</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2">
+        <v>3</v>
+      </c>
+      <c r="E11" s="2">
+        <v>5</v>
+      </c>
+      <c r="F11" s="2">
+        <v>5</v>
+      </c>
+      <c r="G11" s="2">
+        <v>5</v>
+      </c>
+      <c r="H11" s="2">
+        <v>5</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2">
+        <v>5</v>
+      </c>
+      <c r="K11" s="2">
+        <v>3</v>
+      </c>
+      <c r="L11" s="2">
+        <v>5</v>
+      </c>
+      <c r="M11" s="2">
+        <v>1</v>
+      </c>
+      <c r="N11" s="2">
         <v>4</v>
       </c>
-      <c r="C11" s="2">
-        <v>1</v>
-      </c>
-      <c r="D11" s="2">
-        <v>3</v>
-      </c>
-      <c r="E11" s="2">
-        <v>5</v>
-      </c>
-      <c r="F11" s="2">
-        <v>5</v>
-      </c>
-      <c r="G11" s="2">
-        <v>5</v>
-      </c>
-      <c r="H11" s="2">
-        <v>5</v>
-      </c>
-      <c r="I11" s="2">
-        <v>1</v>
-      </c>
-      <c r="J11" s="2">
-        <v>5</v>
-      </c>
-      <c r="K11" s="2">
+      <c r="O11" s="2">
+        <v>3</v>
+      </c>
+      <c r="P11" s="2">
+        <v>5</v>
+      </c>
+      <c r="Q11" s="2">
         <v>4</v>
       </c>
-      <c r="L11" s="2">
-        <v>5</v>
-      </c>
-      <c r="M11" s="2">
-        <v>1</v>
-      </c>
-      <c r="N11" s="2">
-        <v>3</v>
-      </c>
-      <c r="O11" s="2">
-        <v>5</v>
-      </c>
-      <c r="P11" s="2">
-        <v>5</v>
-      </c>
-      <c r="Q11" s="2">
-        <v>1</v>
-      </c>
       <c r="R11" s="2">
         <v>1</v>
       </c>
@@ -2342,16 +2342,16 @@
         <v>5</v>
       </c>
       <c r="W11" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="X11" s="2">
         <v>5</v>
       </c>
       <c r="Y11" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z11" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA11" s="2">
         <v>5</v>
@@ -2378,58 +2378,58 @@
   <sheetData>
     <row r="1" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S1" s="2" t="s">
         <v>44</v>
@@ -2438,45 +2438,45 @@
         <v>45</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W1" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Y1" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Z1" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AA1" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AB1" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AC1" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" s="2">
-        <v>5.2325056433408603</v>
+        <v>4.9109442060085797</v>
       </c>
       <c r="C2" s="2">
         <v>0</v>
       </c>
       <c r="D2" s="2">
-        <v>1.3340857787810401</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2">
         <v>1</v>
@@ -2485,19 +2485,19 @@
         <v>0</v>
       </c>
       <c r="G2" s="2">
-        <v>0.51724137931034497</v>
+        <v>0.99960505529225896</v>
       </c>
       <c r="H2" s="2">
-        <v>0.13468773513920199</v>
+        <v>0.99570815450643702</v>
       </c>
       <c r="I2" s="2">
         <v>0</v>
       </c>
       <c r="J2" s="2">
-        <v>0</v>
+        <v>0.72340425531914898</v>
       </c>
       <c r="K2" s="2">
-        <v>0</v>
+        <v>3.4206008583690899</v>
       </c>
       <c r="L2" s="2">
         <v>0</v>
@@ -2506,16 +2506,16 @@
         <v>0</v>
       </c>
       <c r="N2" s="2">
-        <v>0.33408577878103801</v>
+        <v>0</v>
       </c>
       <c r="O2" s="2">
-        <v>0.86531226486079804</v>
+        <v>4.29184549356223E-3</v>
       </c>
       <c r="P2" s="2">
-        <v>0.49360421369450702</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.51015801354401802</v>
+        <v>0.99892703862660903</v>
       </c>
       <c r="R2" s="2" t="b">
         <v>0</v>
@@ -2530,22 +2530,22 @@
         <v>0</v>
       </c>
       <c r="V2" s="2">
-        <v>1.1745673438675699</v>
+        <v>1</v>
       </c>
       <c r="W2" s="2">
-        <v>10.9954853273138</v>
+        <v>3.9355287569573201</v>
       </c>
       <c r="X2" s="2">
-        <v>0.84848484848484895</v>
+        <v>0.99168399168399102</v>
       </c>
       <c r="Y2" s="2">
-        <v>3.92325056433409</v>
+        <v>1.0729613733905499E-3</v>
       </c>
       <c r="Z2" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA2" s="2">
-        <v>1.6178696310213501E-3</v>
+        <v>1.20336943441636E-3</v>
       </c>
       <c r="AB2" s="2">
         <v>0</v>
@@ -2556,10 +2556,10 @@
     </row>
     <row r="3" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B3" s="2">
-        <v>2.4927246790299602</v>
+        <v>1.9990497307570401</v>
       </c>
       <c r="C3" s="2">
         <v>0</v>
@@ -2574,19 +2574,19 @@
         <v>0</v>
       </c>
       <c r="G3" s="2">
-        <v>0.33596085892905703</v>
+        <v>0.99853372434017595</v>
       </c>
       <c r="H3" s="2">
-        <v>0.27817403708987198</v>
+        <v>0.99904973075704695</v>
       </c>
       <c r="I3" s="2">
         <v>0</v>
       </c>
       <c r="J3" s="2">
-        <v>0</v>
+        <v>0.40275229357798098</v>
       </c>
       <c r="K3" s="2">
-        <v>0</v>
+        <v>5.70161545771301E-2</v>
       </c>
       <c r="L3" s="2">
         <v>0</v>
@@ -2598,13 +2598,13 @@
         <v>0</v>
       </c>
       <c r="O3" s="2">
-        <v>0.72182596291012802</v>
+        <v>9.5026924295216902E-4</v>
       </c>
       <c r="P3" s="2">
-        <v>0.69643366619115599</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.74835948644793104</v>
+        <v>1</v>
       </c>
       <c r="R3" s="2" t="b">
         <v>0</v>
@@ -2619,22 +2619,22 @@
         <v>0</v>
       </c>
       <c r="V3" s="2">
-        <v>0.30356633380884501</v>
+        <v>1</v>
       </c>
       <c r="W3" s="2">
-        <v>14.0984308131241</v>
+        <v>5.1044776119402897</v>
       </c>
       <c r="X3" s="2">
-        <v>0.86111111111111105</v>
+        <v>0.99902375528799203</v>
       </c>
       <c r="Y3" s="2">
-        <v>1.9109843081312401</v>
+        <v>0</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.96633380884450804</v>
+        <v>0</v>
       </c>
       <c r="AA3" s="2">
-        <v>6.1872179356529304E-4</v>
+        <v>2.8083971073509698E-4</v>
       </c>
       <c r="AB3" s="2">
         <v>0</v>
@@ -2645,16 +2645,16 @@
     </row>
     <row r="4" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B4" s="2">
-        <v>7.9067320552830997</v>
+        <v>2.6345905172413699</v>
       </c>
       <c r="C4" s="2">
         <v>0</v>
       </c>
       <c r="D4" s="2">
-        <v>1.16032099866251</v>
+        <v>1</v>
       </c>
       <c r="E4" s="2">
         <v>1</v>
@@ -2663,19 +2663,19 @@
         <v>0</v>
       </c>
       <c r="G4" s="2">
-        <v>0.99866559914598296</v>
+        <v>0.90847788907891502</v>
       </c>
       <c r="H4" s="2">
-        <v>0.67454302273740496</v>
+        <v>0.99935344827586203</v>
       </c>
       <c r="I4" s="2">
         <v>0</v>
       </c>
       <c r="J4" s="2">
-        <v>0</v>
+        <v>0.64556217368924096</v>
       </c>
       <c r="K4" s="2">
-        <v>0</v>
+        <v>0.98750000000000004</v>
       </c>
       <c r="L4" s="2">
         <v>0</v>
@@ -2684,16 +2684,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="2">
-        <v>0.16032099866250599</v>
+        <v>0</v>
       </c>
       <c r="O4" s="2">
-        <v>0.32545697726259498</v>
+        <v>6.4655172413793103E-4</v>
       </c>
       <c r="P4" s="2">
-        <v>1.78332590280874E-4</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.19589835042354001</v>
+        <v>1</v>
       </c>
       <c r="R4" s="2" t="b">
         <v>0</v>
@@ -2708,22 +2708,22 @@
         <v>0</v>
       </c>
       <c r="V4" s="2">
-        <v>1.3204636647347301</v>
+        <v>1</v>
       </c>
       <c r="W4" s="2">
-        <v>6.5213553276861296</v>
+        <v>4.01500636801594</v>
       </c>
       <c r="X4" s="2">
-        <v>0.92307692307692302</v>
+        <v>0.99932990842081704</v>
       </c>
       <c r="Y4" s="2">
-        <v>5.9117253678109698</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="2">
-        <v>0.91850200624164102</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="2">
-        <v>1.14524579837948E-4</v>
+        <v>1.9224607497596901E-4</v>
       </c>
       <c r="AB4" s="2">
         <v>0</v>
@@ -2734,16 +2734,16 @@
     </row>
     <row r="5" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2">
-        <v>7.72536079483646</v>
+        <v>4.0150247193325699</v>
       </c>
       <c r="C5" s="2">
         <v>0</v>
       </c>
       <c r="D5" s="2">
-        <v>1.1596925085212899</v>
+        <v>1</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
@@ -2752,19 +2752,19 @@
         <v>0</v>
       </c>
       <c r="G5" s="2">
-        <v>0.99916684778671305</v>
+        <v>0.98711383352721205</v>
       </c>
       <c r="H5" s="2">
-        <v>0.63568786714047398</v>
+        <v>0.99977469358327298</v>
       </c>
       <c r="I5" s="2">
         <v>0</v>
       </c>
       <c r="J5" s="2">
-        <v>0</v>
+        <v>2.3905921044435799E-2</v>
       </c>
       <c r="K5" s="2">
-        <v>0</v>
+        <v>2.5181275105572101</v>
       </c>
       <c r="L5" s="2">
         <v>0</v>
@@ -2773,16 +2773,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="2">
-        <v>0.159692508521285</v>
+        <v>0</v>
       </c>
       <c r="O5" s="2">
-        <v>0.36431213285952602</v>
+        <v>2.2530641672674801E-4</v>
       </c>
       <c r="P5" s="2">
-        <v>3.6260787584306298E-4</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.20723040104431101</v>
+        <v>0.99998712534761502</v>
       </c>
       <c r="R5" s="2" t="b">
         <v>0</v>
@@ -2797,22 +2797,22 @@
         <v>0</v>
       </c>
       <c r="V5" s="2">
-        <v>1.31902240916673</v>
+        <v>1</v>
       </c>
       <c r="W5" s="2">
-        <v>6.5676263688447296</v>
+        <v>7.8990735265129102</v>
       </c>
       <c r="X5" s="2">
-        <v>0.92857142857142905</v>
-      </c>
-      <c r="Y5" s="2">
-        <v>5.7706505185292603</v>
+        <v>0.99992208702878804</v>
+      </c>
+      <c r="Y5" s="4">
+        <v>1.2874652384385601E-5</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.89578649648270403</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="4">
-        <v>4.5405329887185199E-5</v>
+        <v>1.20830975944685E-5</v>
       </c>
       <c r="AB5" s="2">
         <v>0</v>
@@ -2823,16 +2823,16 @@
     </row>
     <row r="6" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B6" s="2">
-        <v>6.9453952730236397</v>
+        <v>3.8715036338351001</v>
       </c>
       <c r="C6" s="2">
         <v>0</v>
       </c>
       <c r="D6" s="2">
-        <v>1.1435696821515899</v>
+        <v>1</v>
       </c>
       <c r="E6" s="2">
         <v>1</v>
@@ -2841,19 +2841,19 @@
         <v>0</v>
       </c>
       <c r="G6" s="2">
-        <v>0.89889825016202196</v>
+        <v>0.98829128948845002</v>
       </c>
       <c r="H6" s="2">
-        <v>0.57150774246128799</v>
+        <v>0.99977888593423603</v>
       </c>
       <c r="I6" s="2">
         <v>0</v>
       </c>
       <c r="J6" s="2">
-        <v>0</v>
+        <v>7.5652960263843799E-2</v>
       </c>
       <c r="K6" s="2">
-        <v>0</v>
+        <v>2.3501399419284601</v>
       </c>
       <c r="L6" s="2">
         <v>0</v>
@@ -2862,16 +2862,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="2">
-        <v>0.143569682151589</v>
+        <v>0</v>
       </c>
       <c r="O6" s="2">
-        <v>0.42849225753871201</v>
+        <v>2.2111406576397799E-4</v>
       </c>
       <c r="P6" s="2">
-        <v>0.101287693561532</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.28726976365118201</v>
+        <v>0.99998254362638705</v>
       </c>
       <c r="R6" s="2" t="b">
         <v>0</v>
@@ -2886,22 +2886,22 @@
         <v>0</v>
       </c>
       <c r="V6" s="2">
-        <v>1.18585167074165</v>
+        <v>1</v>
       </c>
       <c r="W6" s="2">
-        <v>7.6165933170334101</v>
+        <v>7.6217033212641301</v>
       </c>
       <c r="X6" s="2">
-        <v>0.90566037735849103</v>
-      </c>
-      <c r="Y6" s="2">
-        <v>5.1880358598207001</v>
+        <v>0.99992941093424603</v>
+      </c>
+      <c r="Y6" s="4">
+        <v>1.7456373612945601E-5</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.90630806845965795</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="4">
-        <v>8.1646113725031898E-5</v>
+        <v>1.56093601528156E-5</v>
       </c>
       <c r="AB6" s="2">
         <v>0</v>
@@ -2912,16 +2912,16 @@
     </row>
     <row r="7" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>4.9109442060085797</v>
+        <v>5.2325056433408603</v>
       </c>
       <c r="C7" s="2">
         <v>0</v>
       </c>
       <c r="D7" s="2">
-        <v>1</v>
+        <v>1.3340857787810401</v>
       </c>
       <c r="E7" s="2">
         <v>1</v>
@@ -2930,19 +2930,19 @@
         <v>0</v>
       </c>
       <c r="G7" s="2">
-        <v>0.99960505529225896</v>
+        <v>0.51724137931034497</v>
       </c>
       <c r="H7" s="2">
-        <v>0.99570815450643702</v>
+        <v>0.13468773513920199</v>
       </c>
       <c r="I7" s="2">
         <v>0</v>
       </c>
       <c r="J7" s="2">
-        <v>0.72340425531914898</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2">
-        <v>3.4206008583690899</v>
+        <v>0</v>
       </c>
       <c r="L7" s="2">
         <v>0</v>
@@ -2951,16 +2951,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="2">
-        <v>0</v>
+        <v>0.33408577878103801</v>
       </c>
       <c r="O7" s="2">
-        <v>4.29184549356223E-3</v>
+        <v>0.86531226486079804</v>
       </c>
       <c r="P7" s="2">
-        <v>0</v>
+        <v>0.49360421369450702</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.99892703862660903</v>
+        <v>0.51015801354401802</v>
       </c>
       <c r="R7" s="2" t="b">
         <v>0</v>
@@ -2975,22 +2975,22 @@
         <v>0</v>
       </c>
       <c r="V7" s="2">
-        <v>1</v>
+        <v>1.1745673438675699</v>
       </c>
       <c r="W7" s="2">
-        <v>3.9355287569573201</v>
+        <v>10.9954853273138</v>
       </c>
       <c r="X7" s="2">
-        <v>0.99168399168399102</v>
+        <v>0.84848484848484895</v>
       </c>
       <c r="Y7" s="2">
-        <v>1.0729613733905499E-3</v>
+        <v>3.92325056433409</v>
       </c>
       <c r="Z7" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA7" s="2">
-        <v>1.20336943441636E-3</v>
+        <v>1.6178696310213501E-3</v>
       </c>
       <c r="AB7" s="2">
         <v>0</v>
@@ -3004,7 +3004,7 @@
         <v>59</v>
       </c>
       <c r="B8" s="2">
-        <v>1.9990497307570401</v>
+        <v>2.4927246790299602</v>
       </c>
       <c r="C8" s="2">
         <v>0</v>
@@ -3019,19 +3019,19 @@
         <v>0</v>
       </c>
       <c r="G8" s="2">
-        <v>0.99853372434017595</v>
+        <v>0.33596085892905703</v>
       </c>
       <c r="H8" s="2">
-        <v>0.99904973075704695</v>
+        <v>0.27817403708987198</v>
       </c>
       <c r="I8" s="2">
         <v>0</v>
       </c>
       <c r="J8" s="2">
-        <v>0.40275229357798098</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2">
-        <v>5.70161545771301E-2</v>
+        <v>0</v>
       </c>
       <c r="L8" s="2">
         <v>0</v>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="O8" s="2">
-        <v>9.5026924295216902E-4</v>
+        <v>0.72182596291012802</v>
       </c>
       <c r="P8" s="2">
-        <v>0</v>
+        <v>0.69643366619115599</v>
       </c>
       <c r="Q8" s="2">
-        <v>1</v>
+        <v>0.74835948644793104</v>
       </c>
       <c r="R8" s="2" t="b">
         <v>0</v>
@@ -3064,22 +3064,22 @@
         <v>0</v>
       </c>
       <c r="V8" s="2">
-        <v>1</v>
+        <v>0.30356633380884501</v>
       </c>
       <c r="W8" s="2">
-        <v>5.1044776119402897</v>
+        <v>14.0984308131241</v>
       </c>
       <c r="X8" s="2">
-        <v>0.99902375528799203</v>
+        <v>0.86111111111111105</v>
       </c>
       <c r="Y8" s="2">
-        <v>0</v>
+        <v>1.9109843081312401</v>
       </c>
       <c r="Z8" s="2">
-        <v>0</v>
+        <v>0.96633380884450804</v>
       </c>
       <c r="AA8" s="2">
-        <v>2.8083971073509698E-4</v>
+        <v>6.1872179356529304E-4</v>
       </c>
       <c r="AB8" s="2">
         <v>0</v>
@@ -3093,13 +3093,13 @@
         <v>60</v>
       </c>
       <c r="B9" s="2">
-        <v>2.6345905172413699</v>
+        <v>7.9067320552830997</v>
       </c>
       <c r="C9" s="2">
         <v>0</v>
       </c>
       <c r="D9" s="2">
-        <v>1</v>
+        <v>1.16032099866251</v>
       </c>
       <c r="E9" s="2">
         <v>1</v>
@@ -3108,19 +3108,19 @@
         <v>0</v>
       </c>
       <c r="G9" s="2">
-        <v>0.90847788907891502</v>
+        <v>0.99866559914598296</v>
       </c>
       <c r="H9" s="2">
-        <v>0.99935344827586203</v>
+        <v>0.67454302273740496</v>
       </c>
       <c r="I9" s="2">
         <v>0</v>
       </c>
       <c r="J9" s="2">
-        <v>0.64556217368924096</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2">
-        <v>0.98750000000000004</v>
+        <v>0</v>
       </c>
       <c r="L9" s="2">
         <v>0</v>
@@ -3129,16 +3129,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="2">
-        <v>0</v>
+        <v>0.16032099866250599</v>
       </c>
       <c r="O9" s="2">
-        <v>6.4655172413793103E-4</v>
+        <v>0.32545697726259498</v>
       </c>
       <c r="P9" s="2">
-        <v>0</v>
+        <v>1.78332590280874E-4</v>
       </c>
       <c r="Q9" s="2">
-        <v>1</v>
+        <v>0.19589835042354001</v>
       </c>
       <c r="R9" s="2" t="b">
         <v>0</v>
@@ -3153,22 +3153,22 @@
         <v>0</v>
       </c>
       <c r="V9" s="2">
-        <v>1</v>
+        <v>1.3204636647347301</v>
       </c>
       <c r="W9" s="2">
-        <v>4.01500636801594</v>
+        <v>6.5213553276861296</v>
       </c>
       <c r="X9" s="2">
-        <v>0.99932990842081704</v>
+        <v>0.92307692307692302</v>
       </c>
       <c r="Y9" s="2">
-        <v>0</v>
+        <v>5.9117253678109698</v>
       </c>
       <c r="Z9" s="2">
-        <v>0</v>
+        <v>0.91850200624164102</v>
       </c>
       <c r="AA9" s="2">
-        <v>1.9224607497596901E-4</v>
+        <v>1.14524579837948E-4</v>
       </c>
       <c r="AB9" s="2">
         <v>0</v>
@@ -3182,13 +3182,13 @@
         <v>61</v>
       </c>
       <c r="B10" s="2">
-        <v>4.0150247193325699</v>
+        <v>7.72536079483646</v>
       </c>
       <c r="C10" s="2">
         <v>0</v>
       </c>
       <c r="D10" s="2">
-        <v>1</v>
+        <v>1.1596925085212899</v>
       </c>
       <c r="E10" s="2">
         <v>1</v>
@@ -3197,19 +3197,19 @@
         <v>0</v>
       </c>
       <c r="G10" s="2">
-        <v>0.98711383352721205</v>
+        <v>0.99916684778671305</v>
       </c>
       <c r="H10" s="2">
-        <v>0.99977469358327298</v>
+        <v>0.63568786714047398</v>
       </c>
       <c r="I10" s="2">
         <v>0</v>
       </c>
       <c r="J10" s="2">
-        <v>2.3905921044435799E-2</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2">
-        <v>2.5181275105572101</v>
+        <v>0</v>
       </c>
       <c r="L10" s="2">
         <v>0</v>
@@ -3218,16 +3218,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="2">
-        <v>0</v>
+        <v>0.159692508521285</v>
       </c>
       <c r="O10" s="2">
-        <v>2.2530641672674801E-4</v>
+        <v>0.36431213285952602</v>
       </c>
       <c r="P10" s="2">
-        <v>0</v>
+        <v>3.6260787584306298E-4</v>
       </c>
       <c r="Q10" s="2">
-        <v>0.99998712534761502</v>
+        <v>0.20723040104431101</v>
       </c>
       <c r="R10" s="2" t="b">
         <v>0</v>
@@ -3242,22 +3242,22 @@
         <v>0</v>
       </c>
       <c r="V10" s="2">
-        <v>1</v>
+        <v>1.31902240916673</v>
       </c>
       <c r="W10" s="2">
-        <v>7.8990735265129102</v>
+        <v>6.5676263688447296</v>
       </c>
       <c r="X10" s="2">
-        <v>0.99992208702878804</v>
-      </c>
-      <c r="Y10" s="4">
-        <v>1.2874652384385601E-5</v>
+        <v>0.92857142857142905</v>
+      </c>
+      <c r="Y10" s="2">
+        <v>5.7706505185292603</v>
       </c>
       <c r="Z10" s="2">
-        <v>0</v>
+        <v>0.89578649648270403</v>
       </c>
       <c r="AA10" s="4">
-        <v>1.20830975944685E-5</v>
+        <v>4.5405329887185199E-5</v>
       </c>
       <c r="AB10" s="2">
         <v>0</v>
@@ -3271,13 +3271,13 @@
         <v>62</v>
       </c>
       <c r="B11" s="2">
-        <v>3.8715036338351001</v>
+        <v>6.9453952730236397</v>
       </c>
       <c r="C11" s="2">
         <v>0</v>
       </c>
       <c r="D11" s="2">
-        <v>1</v>
+        <v>1.1435696821515899</v>
       </c>
       <c r="E11" s="2">
         <v>1</v>
@@ -3286,19 +3286,19 @@
         <v>0</v>
       </c>
       <c r="G11" s="2">
-        <v>0.98829128948845002</v>
+        <v>0.89889825016202196</v>
       </c>
       <c r="H11" s="2">
-        <v>0.99977888593423603</v>
+        <v>0.57150774246128799</v>
       </c>
       <c r="I11" s="2">
         <v>0</v>
       </c>
       <c r="J11" s="2">
-        <v>7.5652960263843799E-2</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2">
-        <v>2.3501399419284601</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2">
         <v>0</v>
@@ -3307,16 +3307,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="2">
-        <v>0</v>
+        <v>0.143569682151589</v>
       </c>
       <c r="O11" s="2">
-        <v>2.2111406576397799E-4</v>
+        <v>0.42849225753871201</v>
       </c>
       <c r="P11" s="2">
-        <v>0</v>
+        <v>0.101287693561532</v>
       </c>
       <c r="Q11" s="2">
-        <v>0.99998254362638705</v>
+        <v>0.28726976365118201</v>
       </c>
       <c r="R11" s="2" t="b">
         <v>0</v>
@@ -3331,22 +3331,22 @@
         <v>0</v>
       </c>
       <c r="V11" s="2">
-        <v>1</v>
+        <v>1.18585167074165</v>
       </c>
       <c r="W11" s="2">
-        <v>7.6217033212641301</v>
+        <v>7.6165933170334101</v>
       </c>
       <c r="X11" s="2">
-        <v>0.99992941093424603</v>
-      </c>
-      <c r="Y11" s="4">
-        <v>1.7456373612945601E-5</v>
+        <v>0.90566037735849103</v>
+      </c>
+      <c r="Y11" s="2">
+        <v>5.1880358598207001</v>
       </c>
       <c r="Z11" s="2">
-        <v>0</v>
+        <v>0.90630806845965795</v>
       </c>
       <c r="AA11" s="4">
-        <v>1.56093601528156E-5</v>
+        <v>8.1646113725031898E-5</v>
       </c>
       <c r="AB11" s="2">
         <v>0</v>
